--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
@@ -539,17 +539,17 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Regular price
-                  £10.45</t>
+                  £10.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -661,17 +661,17 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £11.97</t>
+                  £11.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.97</t>
+          <t>£11.80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -783,17 +783,17 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.25</t>
+                  £15.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.25</t>
+          <t>£15.10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.50</t>
+                  £15.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.40</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1027,17 +1027,17 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Regular price
-                  £19.80</t>
+                  £19.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.80</t>
+          <t>£19.60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1149,17 +1149,17 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.70</t>
+                  £21.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.70</t>
+          <t>£21.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.90</t>
+                  £21.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.90</t>
+          <t>£21.60</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1393,17 +1393,17 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £25.15</t>
+                  £24.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£25.15</t>
+          <t>£24.86</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1515,17 +1515,17 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £27.25</t>
+                  £26.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£27.25</t>
+          <t>£26.95</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.79</t>
+                  £26.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1759,7 +1759,7 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Regular price
-                  £35.55</t>
+                  £35.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1881,7 +1881,7 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.89</t>
+                  £32.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2003,7 +2003,7 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.15</t>
+                  £39.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£39.78</t>
+          <t>£39.75</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2246,7 +2246,7 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £40.85</t>
+                  £40.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£43.75</t>
+          <t>£43.70</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£43.75</t>
+          <t>£43.70</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>£68.48</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f51eb5+80197]
-	GetHandleVerifier [0x0x7ff754f51f10+80288]
-	(No symbol) [0x0x7ff754cd02fa]
-	(No symbol) [0x0x7ff754d27cd7]
-	(No symbol) [0x0x7ff754d27f9c]
-	(No symbol) [0x0x7ff754d7ba87]
-	(No symbol) [0x0x7ff754d503bf]
-	(No symbol) [0x0x7ff754d787fb]
-	(No symbol) [0x0x7ff754d50153]
-	(No symbol) [0x0x7ff754d18b02]
-	(No symbol) [0x0x7ff754d198d3]
-	GetHandleVerifier [0x0x7ff75520e83d+2949837]
-	GetHandleVerifier [0x0x7ff755208c6a+2926330]
-	GetHandleVerifier [0x0x7ff7552286c7+3055959]
-	GetHandleVerifier [0x0x7ff754f6cfee+191102]
-	GetHandleVerifier [0x0x7ff754f750af+224063]
-	GetHandleVerifier [0x0x7ff754f5af64+117236]
-	GetHandleVerifier [0x0x7ff754f5b119+117673]
-	GetHandleVerifier [0x0x7ff754f410a8+11064]
+	GetHandleVerifier [0x0x7ff692551eb5+80197]
+	GetHandleVerifier [0x0x7ff692551f10+80288]
+	(No symbol) [0x0x7ff6922d02fa]
+	(No symbol) [0x0x7ff692327cd7]
+	(No symbol) [0x0x7ff692327f9c]
+	(No symbol) [0x0x7ff69237ba87]
+	(No symbol) [0x0x7ff6923503bf]
+	(No symbol) [0x0x7ff6923787fb]
+	(No symbol) [0x0x7ff692350153]
+	(No symbol) [0x0x7ff692318b02]
+	(No symbol) [0x0x7ff6923198d3]
+	GetHandleVerifier [0x0x7ff69280e83d+2949837]
+	GetHandleVerifier [0x0x7ff692808c6a+2926330]
+	GetHandleVerifier [0x0x7ff6928286c7+3055959]
+	GetHandleVerifier [0x0x7ff69256cfee+191102]
+	GetHandleVerifier [0x0x7ff6925750af+224063]
+	GetHandleVerifier [0x0x7ff69255af64+117236]
+	GetHandleVerifier [0x0x7ff69255b119+117673]
+	GetHandleVerifier [0x0x7ff6925410a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.89</t>
+          <t>£32.49</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 520 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£39.76</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.39</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£40.85</t>
+          <t>£40.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>£43.70</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>£43.75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£68.48</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£42.95</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff692551eb5+80197]
-	GetHandleVerifier [0x0x7ff692551f10+80288]
-	(No symbol) [0x0x7ff6922d02fa]
-	(No symbol) [0x0x7ff692327cd7]
-	(No symbol) [0x0x7ff692327f9c]
-	(No symbol) [0x0x7ff69237ba87]
-	(No symbol) [0x0x7ff6923503bf]
-	(No symbol) [0x0x7ff6923787fb]
-	(No symbol) [0x0x7ff692350153]
-	(No symbol) [0x0x7ff692318b02]
-	(No symbol) [0x0x7ff6923198d3]
-	GetHandleVerifier [0x0x7ff69280e83d+2949837]
-	GetHandleVerifier [0x0x7ff692808c6a+2926330]
-	GetHandleVerifier [0x0x7ff6928286c7+3055959]
-	GetHandleVerifier [0x0x7ff69256cfee+191102]
-	GetHandleVerifier [0x0x7ff6925750af+224063]
-	GetHandleVerifier [0x0x7ff69255af64+117236]
-	GetHandleVerifier [0x0x7ff69255b119+117673]
-	GetHandleVerifier [0x0x7ff6925410a8+11064]
+	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
+	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
+	(No symbol) [0x0x7ff7d19802fa]
+	(No symbol) [0x0x7ff7d19d7cd7]
+	(No symbol) [0x0x7ff7d19d7f9c]
+	(No symbol) [0x0x7ff7d1a2ba87]
+	(No symbol) [0x0x7ff7d1a003bf]
+	(No symbol) [0x0x7ff7d1a287fb]
+	(No symbol) [0x0x7ff7d1a00153]
+	(No symbol) [0x0x7ff7d19c8b02]
+	(No symbol) [0x0x7ff7d19c98d3]
+	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
+	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
+	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
+	GetHandleVerifier [0x0x7ff7d1c250af+224063]
+	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
+	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
+	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1271,7 +1271,7 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.60</t>
+                  £21.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>£39.47</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£35.13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 520 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£43.75</t>
+          <t>£43.70</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.208); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7d1c01eb5+80197]
-	GetHandleVerifier [0x0x7ff7d1c01f10+80288]
-	(No symbol) [0x0x7ff7d19802fa]
-	(No symbol) [0x0x7ff7d19d7cd7]
-	(No symbol) [0x0x7ff7d19d7f9c]
-	(No symbol) [0x0x7ff7d1a2ba87]
-	(No symbol) [0x0x7ff7d1a003bf]
-	(No symbol) [0x0x7ff7d1a287fb]
-	(No symbol) [0x0x7ff7d1a00153]
-	(No symbol) [0x0x7ff7d19c8b02]
-	(No symbol) [0x0x7ff7d19c98d3]
-	GetHandleVerifier [0x0x7ff7d1ebe83d+2949837]
-	GetHandleVerifier [0x0x7ff7d1eb8c6a+2926330]
-	GetHandleVerifier [0x0x7ff7d1ed86c7+3055959]
-	GetHandleVerifier [0x0x7ff7d1c1cfee+191102]
-	GetHandleVerifier [0x0x7ff7d1c250af+224063]
-	GetHandleVerifier [0x0x7ff7d1c0af64+117236]
-	GetHandleVerifier [0x0x7ff7d1c0b119+117673]
-	GetHandleVerifier [0x0x7ff7d1bf10a8+11064]
+	GetHandleVerifier [0x0x7ff62d9f1eb5+80197]
+	GetHandleVerifier [0x0x7ff62d9f1f10+80288]
+	(No symbol) [0x0x7ff62d7702fa]
+	(No symbol) [0x0x7ff62d7c7cd7]
+	(No symbol) [0x0x7ff62d7c7f9c]
+	(No symbol) [0x0x7ff62d81ba87]
+	(No symbol) [0x0x7ff62d7f03bf]
+	(No symbol) [0x0x7ff62d8187fb]
+	(No symbol) [0x0x7ff62d7f0153]
+	(No symbol) [0x0x7ff62d7b8b02]
+	(No symbol) [0x0x7ff62d7b98d3]
+	GetHandleVerifier [0x0x7ff62dcae83d+2949837]
+	GetHandleVerifier [0x0x7ff62dca8c6a+2926330]
+	GetHandleVerifier [0x0x7ff62dcc86c7+3055959]
+	GetHandleVerifier [0x0x7ff62da0cfee+191102]
+	GetHandleVerifier [0x0x7ff62da150af+224063]
+	GetHandleVerifier [0x0x7ff62d9faf64+117236]
+	GetHandleVerifier [0x0x7ff62d9fb119+117673]
+	GetHandleVerifier [0x0x7ff62d9e10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
